--- a/door_switch_maze/grid/DQN/episode_rewards.xlsx
+++ b/door_switch_maze/grid/DQN/episode_rewards.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B501"/>
+  <dimension ref="A1:B511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4440,6 +4440,86 @@
         <v>0.3334375000000001</v>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>501</v>
+      </c>
+      <c r="B502" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>502</v>
+      </c>
+      <c r="B503" t="n">
+        <v>0.881875</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>503</v>
+      </c>
+      <c r="B504" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>504</v>
+      </c>
+      <c r="B505" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>505</v>
+      </c>
+      <c r="B506" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>506</v>
+      </c>
+      <c r="B507" t="n">
+        <v>0.74125</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>507</v>
+      </c>
+      <c r="B508" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>508</v>
+      </c>
+      <c r="B509" t="n">
+        <v>0.3629687500000001</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>509</v>
+      </c>
+      <c r="B510" t="n">
+        <v>0.80453125</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>510</v>
+      </c>
+      <c r="B511" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/door_switch_maze/grid/DQN/episode_rewards.xlsx
+++ b/door_switch_maze/grid/DQN/episode_rewards.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B511"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4520,6 +4520,166 @@
         <v>0</v>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>511</v>
+      </c>
+      <c r="B512" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>512</v>
+      </c>
+      <c r="B513" t="n">
+        <v>0.3475</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>513</v>
+      </c>
+      <c r="B514" t="n">
+        <v>0.32640625</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>514</v>
+      </c>
+      <c r="B515" t="n">
+        <v>0.5921875</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>515</v>
+      </c>
+      <c r="B516" t="n">
+        <v>0.41359375</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>516</v>
+      </c>
+      <c r="B517" t="n">
+        <v>0.56265625</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>517</v>
+      </c>
+      <c r="B518" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>518</v>
+      </c>
+      <c r="B519" t="n">
+        <v>0.63578125</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>519</v>
+      </c>
+      <c r="B520" t="n">
+        <v>0.2982812500000001</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>520</v>
+      </c>
+      <c r="B521" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>521</v>
+      </c>
+      <c r="B522" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>522</v>
+      </c>
+      <c r="B523" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>523</v>
+      </c>
+      <c r="B524" t="n">
+        <v>0.5879687499999999</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>524</v>
+      </c>
+      <c r="B525" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>525</v>
+      </c>
+      <c r="B526" t="n">
+        <v>0.7946875</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>526</v>
+      </c>
+      <c r="B527" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>527</v>
+      </c>
+      <c r="B528" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>528</v>
+      </c>
+      <c r="B529" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>529</v>
+      </c>
+      <c r="B530" t="n">
+        <v>0.51625</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>530</v>
+      </c>
+      <c r="B531" t="n">
+        <v>0.48390625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
